--- a/src/main/resources/templates/xlsx/2차전형결과.xlsx
+++ b/src/main/resources/templates/xlsx/2차전형결과.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeon-yujin/Documents/workspace/backend/springboot/maru/src/main/resources/templates/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/main/resources/templates/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F52063-F22D-BF42-8945-86AF738BCAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099DA56F-0C65-FB48-9B1E-D2982786AC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="15000" windowHeight="18900" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="15000" windowHeight="16540" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>수험번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,14 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>코딩 테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>접수번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -94,14 +86,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>봉사활동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가산점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>총점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -110,14 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>심층 면접</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>지원 전형</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,6 +103,14 @@
   </si>
   <si>
     <t>생년월일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기주도학습영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인성영역</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -260,10 +244,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -594,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8EB960-16E4-4546-BE22-CABF45F1D2EB}">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="9.140625" bestFit="1" customWidth="1"/>
@@ -608,17 +592,15 @@
     <col min="10" max="10" width="16.140625" customWidth="1"/>
     <col min="11" max="11" width="16.5703125" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" customWidth="1"/>
-    <col min="20" max="20" width="9.42578125" customWidth="1"/>
+    <col min="13" max="14" width="9" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30" customHeight="1">
+    <row r="1" spans="1:17" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -626,97 +608,80 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6"/>
+      <c r="D1" s="5"/>
       <c r="E1" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="5"/>
       <c r="M1" s="4"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
       <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="30" customHeight="1">
+    <row r="2" spans="1:17" ht="30" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="P9" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="M1:Q1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:L1"/>
-    <mergeCell ref="M1:T1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/templates/xlsx/2차전형결과.xlsx
+++ b/src/main/resources/templates/xlsx/2차전형결과.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/main/resources/templates/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099DA56F-0C65-FB48-9B1E-D2982786AC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCE3755-C300-3B42-A51D-E3E9BB88E080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="15000" windowHeight="16540" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>수험번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,6 +111,10 @@
   </si>
   <si>
     <t>인성영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>면접번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -149,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -222,13 +226,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -238,16 +255,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -578,110 +601,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8EB960-16E4-4546-BE22-CABF45F1D2EB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" customWidth="1"/>
+    <col min="1" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="15" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:18" ht="30" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="5"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="5"/>
     </row>
-    <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="1:18" ht="30" customHeight="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="M1:Q1"/>
+  <mergeCells count="7">
+    <mergeCell ref="N1:R1"/>
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:M1"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:L1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
